--- a/software-quote-builder/assets/quote-sample-preview.xlsx
+++ b/software-quote-builder/assets/quote-sample-preview.xlsx
@@ -163,14 +163,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
@@ -256,14 +256,14 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G3" s="4">
         <v>800</v>
       </c>
       <c r="H3" s="4">
         <f>F3*G3</f>
-        <v>9600</v>
+        <v>13600</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -296,14 +296,14 @@
         </is>
       </c>
       <c r="F4" s="15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G4" s="16">
         <v>800</v>
       </c>
       <c r="H4" s="16">
         <f>F4*G4</f>
-        <v>14400</v>
+        <v>19200</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -336,14 +336,14 @@
         </is>
       </c>
       <c r="F5" s="3">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4">
         <v>800</v>
       </c>
       <c r="H5" s="4">
         <f>F5*G5</f>
-        <v>25600</v>
+        <v>34400</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -376,18 +376,18 @@
         </is>
       </c>
       <c r="F6" s="15">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G6" s="16">
         <v>800</v>
       </c>
       <c r="H6" s="16">
         <f>F6*G6</f>
-        <v>38400</v>
+        <v>51200</v>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">需求说明第 10-12 页</t>
+          <t xml:space="preserve">原型图第 12-14 页</t>
         </is>
       </c>
     </row>
@@ -397,150 +397,102 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">审批中心</t>
+          <t xml:space="preserve">数据分析</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">售后流程</t>
+          <t xml:space="preserve">经营看板</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">退货审批流程</t>
+          <t xml:space="preserve">销售概览</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">发起审批、节点流转、驳回、审批历史、消息提醒</t>
+          <t xml:space="preserve">销售额、订单数、客户数、趋势图与时间筛选</t>
         </is>
       </c>
       <c r="F7" s="3">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4">
         <v>800</v>
       </c>
       <c r="H7" s="4">
         <f>F7*G7</f>
-        <v>44800</v>
+        <v>25600</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">原型图第 15-16 页</t>
+          <t xml:space="preserve">需求说明第 10 页</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="15">
-        <v>6</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">报表中心</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">经营分析</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">销售统计报表</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">销售趋势、门店维度分析、商品维度排行、导出</t>
-        </is>
-      </c>
-      <c r="F8" s="15">
-        <v>38</v>
-      </c>
-      <c r="G8" s="16">
-        <v>800</v>
-      </c>
-      <c r="H8" s="16">
-        <f>F8*G8</f>
-        <v>30400</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">需求说明第 18 页</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合计</t>
+        </is>
+      </c>
+      <c r="F8" s="6">
+        <f>SUM(F3:F7)</f>
+        <v>180</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H8" s="7">
+        <f>SUM(H3:H7)</f>
+        <v>144000</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开放平台</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">接口对接</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERP 订单回传接口</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">订单数据推送、回调处理、失败重试、日志查询</t>
-        </is>
-      </c>
-      <c r="F9" s="3">
-        <v>44</v>
-      </c>
-      <c r="G9" s="4">
-        <v>800</v>
-      </c>
-      <c r="H9" s="4">
-        <f>F9*G9</f>
-        <v>35200</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">按单向对接估算，不含复杂对账</t>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">特殊说明</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合计</t>
-        </is>
-      </c>
-      <c r="F10" s="6">
-        <f>SUM(F3:F9)</f>
-        <v>248</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H10" s="7">
-        <f>SUM(H3:H9)</f>
-        <v>198400</v>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 仅为软件功能开发费用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. 默认包含自项目验收之日起一年的维护期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. 服务器及第三方服务相关费用由客户自行支付。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:I2"/>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
